--- a/artfynd/A 36820-2021 artfynd.xlsx
+++ b/artfynd/A 36820-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36820-2021 artfynd.xlsx
+++ b/artfynd/A 36820-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97365119</v>
+        <v>97365124</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531601.1184696174</v>
+        <v>531544</v>
       </c>
       <c r="R2" t="n">
-        <v>6967421.175263753</v>
+        <v>6967491</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2021-10-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-15</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,6 +756,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -791,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97365088</v>
+        <v>97365126</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531571.7068167335</v>
+        <v>531613</v>
       </c>
       <c r="R3" t="n">
-        <v>6967386.619718896</v>
+        <v>6967348</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,21 +849,11 @@
           <t>2021-10-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-15</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -887,11 +862,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -912,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97365142</v>
+        <v>97365088</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531530.3253629706</v>
+        <v>531571</v>
       </c>
       <c r="R4" t="n">
-        <v>6967502.289156869</v>
+        <v>6967387</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,21 +950,11 @@
           <t>2021-10-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-15</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1011,7 +966,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1033,37 +988,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97365111</v>
+        <v>97365136</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>531597.4357734332</v>
+        <v>531544</v>
       </c>
       <c r="R5" t="n">
-        <v>6967470.94826384</v>
+        <v>6967491</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,21 +1056,11 @@
           <t>2021-10-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1129,6 +1069,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1149,15 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97365124</v>
+        <v>97365142</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,21 +1105,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>531544.1661112118</v>
+        <v>531530</v>
       </c>
       <c r="R6" t="n">
-        <v>6967490.54149941</v>
+        <v>6967502</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,21 +1162,11 @@
           <t>2021-10-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-10-15</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1248,7 +1178,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1270,37 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97365136</v>
+        <v>97365096</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>531544.1661112118</v>
+        <v>531642</v>
       </c>
       <c r="R7" t="n">
-        <v>6967490.54149941</v>
+        <v>6967265</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,21 +1268,11 @@
           <t>2021-10-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-10-15</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1366,11 +1281,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1391,15 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97365096</v>
+        <v>97365099</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>531641.9717258923</v>
+        <v>531553</v>
       </c>
       <c r="R8" t="n">
-        <v>6967265.741354842</v>
+        <v>6967373</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,19 +1369,9 @@
           <t>2021-10-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,37 +1402,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97365126</v>
+        <v>97365111</v>
       </c>
       <c r="B9" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1547,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>531612.8045133791</v>
+        <v>531597</v>
       </c>
       <c r="R9" t="n">
-        <v>6967348.173137488</v>
+        <v>6967471</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,19 +1470,9 @@
           <t>2021-10-14</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,6 +1496,208 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>97365119</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kullan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>531601</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6967421</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>97365158</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kullan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>531563</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6967365</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
